--- a/IEF_Home/UploadedFiles/3_LT_Vehicles_LIST_Sample.xlsx
+++ b/IEF_Home/UploadedFiles/3_LT_Vehicles_LIST_Sample.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20415"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F467931-B270-471B-B158-27553939F1C9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C53144-06F4-440F-80DB-FFECB652A9DD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="1140" windowWidth="20418" windowHeight="13440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -1176,7 +1176,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -1192,7 +1192,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1513,24 +1513,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V72"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.15625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.15625" customWidth="1"/>
-    <col min="2" max="2" width="15.83984375" customWidth="1"/>
-    <col min="3" max="3" width="23.15625" style="37" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="46.83984375" style="37" customWidth="1"/>
-    <col min="5" max="5" width="26.3125" customWidth="1"/>
-    <col min="6" max="6" width="24.3125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" style="37" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46.85546875" style="37" customWidth="1"/>
+    <col min="5" max="5" width="26.28515625" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="26" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.83984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.3125" customWidth="1"/>
+    <col min="9" max="9" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="E1" s="1"/>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" spans="1:11" ht="15.6">
+    <row r="2" spans="1:11" ht="15.75">
       <c r="B2" s="72" t="s">
         <v>22</v>
       </c>
@@ -3077,21 +3077,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83984375" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="27.83984375" style="37" customWidth="1"/>
-    <col min="2" max="2" width="23.3125" style="37" customWidth="1"/>
-    <col min="3" max="3" width="19.47265625" style="37" customWidth="1"/>
-    <col min="4" max="4" width="13.83984375" style="37" customWidth="1"/>
-    <col min="5" max="5" width="15.47265625" style="37" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="17.68359375" style="37" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.68359375" style="37" customWidth="1"/>
-    <col min="9" max="9" width="11.3125" style="37" customWidth="1"/>
-    <col min="10" max="10" width="21.83984375" style="37" customWidth="1"/>
-    <col min="11" max="16384" width="10.83984375" style="37"/>
+    <col min="1" max="1" width="27.85546875" style="37" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="37" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" style="37" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" style="37" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" style="37" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="17.7109375" style="37" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" style="37" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" style="37" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" style="37" customWidth="1"/>
+    <col min="11" max="16384" width="10.85546875" style="37"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="14.1">
+    <row r="1" spans="1:9" ht="15">
       <c r="A1" s="7" t="s">
         <v>116</v>
       </c>

--- a/IEF_Home/UploadedFiles/3_LT_Vehicles_LIST_Sample.xlsx
+++ b/IEF_Home/UploadedFiles/3_LT_Vehicles_LIST_Sample.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20415"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20413"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C53144-06F4-440F-80DB-FFECB652A9DD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F467931-B270-471B-B158-27553939F1C9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="1140" windowWidth="20418" windowHeight="13440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -1176,7 +1176,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -1192,7 +1192,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1513,24 +1513,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V72"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.15625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.140625" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" style="37" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="46.85546875" style="37" customWidth="1"/>
-    <col min="5" max="5" width="26.28515625" customWidth="1"/>
-    <col min="6" max="6" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.15625" customWidth="1"/>
+    <col min="2" max="2" width="15.83984375" customWidth="1"/>
+    <col min="3" max="3" width="23.15625" style="37" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46.83984375" style="37" customWidth="1"/>
+    <col min="5" max="5" width="26.3125" customWidth="1"/>
+    <col min="6" max="6" width="24.3125" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="26" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.28515625" customWidth="1"/>
+    <col min="9" max="9" width="24.83984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.3125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="E1" s="1"/>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" spans="1:11" ht="15.75">
+    <row r="2" spans="1:11" ht="15.6">
       <c r="B2" s="72" t="s">
         <v>22</v>
       </c>
@@ -3077,21 +3077,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I21"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83984375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" style="37" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" style="37" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" style="37" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" style="37" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" style="37" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="17.7109375" style="37" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" style="37" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" style="37" customWidth="1"/>
-    <col min="10" max="10" width="21.85546875" style="37" customWidth="1"/>
-    <col min="11" max="16384" width="10.85546875" style="37"/>
+    <col min="1" max="1" width="27.83984375" style="37" customWidth="1"/>
+    <col min="2" max="2" width="23.3125" style="37" customWidth="1"/>
+    <col min="3" max="3" width="19.47265625" style="37" customWidth="1"/>
+    <col min="4" max="4" width="13.83984375" style="37" customWidth="1"/>
+    <col min="5" max="5" width="15.47265625" style="37" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="17.68359375" style="37" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.68359375" style="37" customWidth="1"/>
+    <col min="9" max="9" width="11.3125" style="37" customWidth="1"/>
+    <col min="10" max="10" width="21.83984375" style="37" customWidth="1"/>
+    <col min="11" max="16384" width="10.83984375" style="37"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15">
+    <row r="1" spans="1:9" ht="14.1">
       <c r="A1" s="7" t="s">
         <v>116</v>
       </c>
